--- a/wolf/Excel/Tab3_三级页签.xlsx
+++ b/wolf/Excel/Tab3_三级页签.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="143">
   <si>
     <t>Int</t>
   </si>
@@ -327,6 +327,12 @@
   </si>
   <si>
     <t>Text_Tab3_1047</t>
+  </si>
+  <si>
+    <t>灵宠</t>
+  </si>
+  <si>
+    <t>Text_Tab3_1048</t>
   </si>
   <si>
     <r>
@@ -1960,7 +1966,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:T272"/>
+  <dimension ref="A1:T273"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="3" width="13" customWidth="1"/>
@@ -3388,7 +3394,7 @@
     </row>
     <row r="52" ht="21" customHeight="1" spans="1:20">
       <c r="A52" s="2">
-        <v>2001</v>
+        <v>1048</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>100</v>
@@ -3416,7 +3422,7 @@
     </row>
     <row r="53" ht="21" customHeight="1" spans="1:20">
       <c r="A53" s="2">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>102</v>
@@ -3444,7 +3450,7 @@
     </row>
     <row r="54" ht="21" customHeight="1" spans="1:20">
       <c r="A54" s="2">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>104</v>
@@ -3472,7 +3478,7 @@
     </row>
     <row r="55" ht="21" customHeight="1" spans="1:20">
       <c r="A55" s="2">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>106</v>
@@ -3500,7 +3506,7 @@
     </row>
     <row r="56" ht="21" customHeight="1" spans="1:20">
       <c r="A56" s="2">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>108</v>
@@ -3528,7 +3534,7 @@
     </row>
     <row r="57" ht="21" customHeight="1" spans="1:20">
       <c r="A57" s="2">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>110</v>
@@ -3556,7 +3562,7 @@
     </row>
     <row r="58" ht="21" customHeight="1" spans="1:20">
       <c r="A58" s="2">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>112</v>
@@ -3584,7 +3590,7 @@
     </row>
     <row r="59" ht="21" customHeight="1" spans="1:20">
       <c r="A59" s="2">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>114</v>
@@ -3612,7 +3618,7 @@
     </row>
     <row r="60" ht="21" customHeight="1" spans="1:20">
       <c r="A60" s="2">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>116</v>
@@ -3640,7 +3646,7 @@
     </row>
     <row r="61" ht="21" customHeight="1" spans="1:20">
       <c r="A61" s="2">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>118</v>
@@ -3668,7 +3674,7 @@
     </row>
     <row r="62" ht="21" customHeight="1" spans="1:20">
       <c r="A62" s="2">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>120</v>
@@ -3696,7 +3702,7 @@
     </row>
     <row r="63" ht="21" customHeight="1" spans="1:20">
       <c r="A63" s="2">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>122</v>
@@ -3724,7 +3730,7 @@
     </row>
     <row r="64" ht="21" customHeight="1" spans="1:20">
       <c r="A64" s="2">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>124</v>
@@ -3752,7 +3758,7 @@
     </row>
     <row r="65" ht="21" customHeight="1" spans="1:20">
       <c r="A65" s="2">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>126</v>
@@ -3780,7 +3786,7 @@
     </row>
     <row r="66" ht="21" customHeight="1" spans="1:20">
       <c r="A66" s="2">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>128</v>
@@ -3808,7 +3814,7 @@
     </row>
     <row r="67" ht="21" customHeight="1" spans="1:20">
       <c r="A67" s="2">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>130</v>
@@ -3836,7 +3842,7 @@
     </row>
     <row r="68" ht="21" customHeight="1" spans="1:20">
       <c r="A68" s="2">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>132</v>
@@ -3864,7 +3870,7 @@
     </row>
     <row r="69" ht="21" customHeight="1" spans="1:20">
       <c r="A69" s="2">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>134</v>
@@ -3892,7 +3898,7 @@
     </row>
     <row r="70" ht="21" customHeight="1" spans="1:20">
       <c r="A70" s="2">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>136</v>
@@ -3920,7 +3926,7 @@
     </row>
     <row r="71" ht="21" customHeight="1" spans="1:20">
       <c r="A71" s="2">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>138</v>
@@ -3946,15 +3952,15 @@
       <c r="S71" s="1"/>
       <c r="T71" s="1"/>
     </row>
-    <row r="72" ht="16" customHeight="1" spans="1:20">
-      <c r="A72" s="1">
-        <v>2021</v>
+    <row r="72" ht="21" customHeight="1" spans="1:20">
+      <c r="A72" s="2">
+        <v>2020</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>140</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>47</v>
+        <v>141</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -3974,10 +3980,16 @@
       <c r="S72" s="1"/>
       <c r="T72" s="1"/>
     </row>
-    <row r="73" spans="1:20">
-      <c r="A73" s="1"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="2"/>
+    <row r="73" ht="16" customHeight="1" spans="1:20">
+      <c r="A73" s="1">
+        <v>2021</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -8374,6 +8386,28 @@
       <c r="S272" s="1"/>
       <c r="T272" s="1"/>
     </row>
+    <row r="273" spans="1:20">
+      <c r="A273" s="1"/>
+      <c r="B273" s="2"/>
+      <c r="C273" s="2"/>
+      <c r="D273" s="1"/>
+      <c r="E273" s="1"/>
+      <c r="F273" s="1"/>
+      <c r="G273" s="1"/>
+      <c r="H273" s="1"/>
+      <c r="I273" s="1"/>
+      <c r="J273" s="1"/>
+      <c r="K273" s="1"/>
+      <c r="L273" s="1"/>
+      <c r="M273" s="1"/>
+      <c r="N273" s="1"/>
+      <c r="O273" s="1"/>
+      <c r="P273" s="1"/>
+      <c r="Q273" s="1"/>
+      <c r="R273" s="1"/>
+      <c r="S273" s="1"/>
+      <c r="T273" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
